--- a/tiflow-erezept/main/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Medication.xlsx
+++ b/tiflow-erezept/main/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Medication.xlsx
@@ -672,6 +672,9 @@
 </t>
   </si>
   <si>
+    <t>Extension</t>
+  </si>
+  <si>
     <t>This extension is used to track medication prescription transactions between the E-Rezept-Fachdienst and the ePA. The RxPrescriptionProcessIdentifier is generated by the ePA Medication Service and consists of the PrescriptionId and the authoredOn date of the operation parameters request. It ensures consistent referencing and management of medication-related resources across different systems.</t>
   </si>
   <si>
@@ -955,9 +958,6 @@
   <si>
     <t xml:space="preserve">Extension {https://gematik.de/fhir/epa-medication/StructureDefinition/medication-manufacturing-instructions-extension}
 </t>
-  </si>
-  <si>
-    <t>Extension</t>
   </si>
   <si>
     <t>Manufacturing instructions regarding the preparation of a formulation (Subscriptio).</t>
@@ -4768,10 +4768,10 @@
         <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>112</v>
@@ -4842,7 +4842,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -4853,13 +4853,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>108</v>
@@ -4881,13 +4881,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>203</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>112</v>
@@ -4969,13 +4969,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>108</v>
@@ -4997,13 +4997,13 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>203</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>112</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5197,10 +5197,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5311,10 +5311,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5340,13 +5340,13 @@
         <v>130</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>78</v>
@@ -5396,7 +5396,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>88</v>
@@ -5425,10 +5425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5454,10 +5454,10 @@
         <v>148</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5484,11 +5484,11 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -5506,7 +5506,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5535,10 +5535,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5647,10 +5647,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5761,10 +5761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5790,16 +5790,16 @@
         <v>130</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5848,7 +5848,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5866,21 +5866,21 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5906,13 +5906,13 @@
         <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5962,7 +5962,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5980,21 +5980,21 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6020,14 +6020,14 @@
         <v>173</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6076,7 +6076,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -6094,21 +6094,21 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6134,16 +6134,16 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -6192,7 +6192,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6210,21 +6210,21 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6247,19 +6247,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -6308,7 +6308,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6326,24 +6326,24 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>108</v>
@@ -6365,13 +6365,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>112</v>
@@ -6453,10 +6453,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6565,10 +6565,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6679,10 +6679,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6708,13 +6708,13 @@
         <v>130</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6764,7 +6764,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -6793,10 +6793,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6822,10 +6822,10 @@
         <v>173</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6852,11 +6852,11 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -6874,7 +6874,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6903,13 +6903,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>108</v>
@@ -6931,13 +6931,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>203</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>112</v>
@@ -7019,13 +7019,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>108</v>
@@ -7047,10 +7047,10 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>301</v>
+        <v>208</v>
       </c>
       <c r="M40" t="s" s="2">
         <v>302</v>
@@ -8538,16 +8538,16 @@
         <v>130</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8596,7 +8596,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8614,13 +8614,13 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -8654,13 +8654,13 @@
         <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8710,7 +8710,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8728,13 +8728,13 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8824,7 +8824,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8842,13 +8842,13 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56">
@@ -8882,16 +8882,16 @@
         <v>102</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8940,7 +8940,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8958,13 +8958,13 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -8995,19 +8995,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -9056,7 +9056,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9074,13 +9074,13 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="58">
@@ -9458,16 +9458,16 @@
         <v>130</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9516,7 +9516,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9534,13 +9534,13 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="62" hidden="true">
@@ -9574,13 +9574,13 @@
         <v>102</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9630,7 +9630,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9648,13 +9648,13 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9744,7 +9744,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9762,13 +9762,13 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="64">
@@ -9802,16 +9802,16 @@
         <v>102</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9860,7 +9860,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9878,13 +9878,13 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="65" hidden="true">
@@ -9915,19 +9915,19 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9976,7 +9976,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9994,13 +9994,13 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="66">
@@ -10378,16 +10378,16 @@
         <v>130</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10436,7 +10436,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10454,13 +10454,13 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70" hidden="true">
@@ -10494,13 +10494,13 @@
         <v>102</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10550,7 +10550,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10568,13 +10568,13 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="71">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10664,7 +10664,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10682,13 +10682,13 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72">
@@ -10722,16 +10722,16 @@
         <v>102</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10780,7 +10780,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10798,13 +10798,13 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -10835,19 +10835,19 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10896,7 +10896,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10914,13 +10914,13 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="74">
@@ -11102,7 +11102,7 @@
         <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y75" t="s" s="2">
         <v>404</v>
@@ -12586,7 +12586,7 @@
         <v>78</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
@@ -12892,16 +12892,16 @@
         <v>130</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -12950,7 +12950,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12968,13 +12968,13 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="92" hidden="true">
@@ -13008,13 +13008,13 @@
         <v>102</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13064,7 +13064,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13082,13 +13082,13 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="93">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -13178,7 +13178,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13196,13 +13196,13 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94">
@@ -13236,16 +13236,16 @@
         <v>102</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>78</v>
@@ -13294,7 +13294,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13312,13 +13312,13 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="95" hidden="true">
@@ -13349,19 +13349,19 @@
         <v>89</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -13410,7 +13410,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13428,13 +13428,13 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="96">
@@ -13504,7 +13504,7 @@
         <v>78</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
@@ -13810,16 +13810,16 @@
         <v>130</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13868,7 +13868,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13886,13 +13886,13 @@
         <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="100" hidden="true">
@@ -13926,13 +13926,13 @@
         <v>102</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13982,7 +13982,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14000,13 +14000,13 @@
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14096,7 +14096,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14114,13 +14114,13 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102">
@@ -14154,16 +14154,16 @@
         <v>102</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14212,7 +14212,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14230,13 +14230,13 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="103" hidden="true">
@@ -14267,19 +14267,19 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14328,7 +14328,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14346,13 +14346,13 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="104">
@@ -15562,7 +15562,7 @@
         <v>78</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y114" t="s" s="2">
         <v>535</v>
@@ -15650,7 +15650,7 @@
         <v>542</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O115" t="s" s="2">
         <v>543</v>
@@ -16480,7 +16480,7 @@
         <v>78</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y122" t="s" s="2">
         <v>535</v>
@@ -16568,7 +16568,7 @@
         <v>542</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>543</v>
@@ -18392,16 +18392,16 @@
         <v>130</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>78</v>
@@ -18450,7 +18450,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -18468,13 +18468,13 @@
         <v>78</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="140" hidden="true">
@@ -18508,13 +18508,13 @@
         <v>102</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -18564,7 +18564,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18582,13 +18582,13 @@
         <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="141">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -18678,7 +18678,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -18696,13 +18696,13 @@
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="142">
@@ -18736,16 +18736,16 @@
         <v>102</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -18794,7 +18794,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18812,13 +18812,13 @@
         <v>78</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" hidden="true">
@@ -18849,19 +18849,19 @@
         <v>89</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -18910,7 +18910,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -18928,13 +18928,13 @@
         <v>78</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="144">
@@ -19312,16 +19312,16 @@
         <v>130</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -19370,7 +19370,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19388,13 +19388,13 @@
         <v>78</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="148" hidden="true">
@@ -19428,13 +19428,13 @@
         <v>102</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19484,7 +19484,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19502,13 +19502,13 @@
         <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="149">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -19598,7 +19598,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -19616,13 +19616,13 @@
         <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="150">
@@ -19656,16 +19656,16 @@
         <v>102</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>78</v>
@@ -19714,7 +19714,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -19732,13 +19732,13 @@
         <v>78</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="151" hidden="true">
@@ -19769,19 +19769,19 @@
         <v>89</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>78</v>
@@ -19830,7 +19830,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -19848,13 +19848,13 @@
         <v>78</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="152">
@@ -20232,16 +20232,16 @@
         <v>130</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>78</v>
@@ -20290,7 +20290,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -20308,13 +20308,13 @@
         <v>78</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="156" hidden="true">
@@ -20348,13 +20348,13 @@
         <v>102</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20404,7 +20404,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -20422,13 +20422,13 @@
         <v>78</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="157">
@@ -20469,7 +20469,7 @@
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>78</v>
@@ -20518,7 +20518,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -20536,13 +20536,13 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="158">
@@ -20576,16 +20576,16 @@
         <v>102</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>78</v>
@@ -20634,7 +20634,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -20652,13 +20652,13 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="159" hidden="true">
@@ -20689,19 +20689,19 @@
         <v>89</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -20750,7 +20750,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -20768,13 +20768,13 @@
         <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="160">
@@ -21039,7 +21039,7 @@
         <v>78</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L162" t="s" s="2">
         <v>649</v>
@@ -22098,7 +22098,7 @@
         <v>78</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y171" t="s" s="2">
         <v>535</v>
@@ -22186,7 +22186,7 @@
         <v>542</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>543</v>
@@ -23016,7 +23016,7 @@
         <v>78</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y179" t="s" s="2">
         <v>535</v>
@@ -23104,7 +23104,7 @@
         <v>542</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O180" t="s" s="2">
         <v>543</v>
@@ -23906,7 +23906,7 @@
         <v>690</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
